--- a/data/trans_bre/IQ09_D_R3-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ09_D_R3-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -522,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que llevan más tiempo (cuartil más desfavorable) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Menores que llevan más tiempo (cuartil más desfavorable: más de 2161 días) sufriendo esa dolencia, enfermedad o impedimento que le haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -610,299 +619,131 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-8,88</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-44,29; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-28,45; 48,42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-8.881044458956588</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.162423575605867</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="n">
+        <v>0.06025213139340447</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-14,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-17,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-44,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>30,49%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-44.2853191346866</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="n">
+        <v>-28.45419455394131</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-54,93; 36,26</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-46,94; 44,06</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-56,92; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-25,8; 42,6</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="n">
+        <v>48.42028933419537</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +751,269 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-17,84</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-13,49</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,67%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-59,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-41,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,38%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-14.82815203256905</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4.222881757451108</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-17.19885821623887</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.222229362989764</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4456394218764559</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.2316987351505389</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3049418880427723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-47,06; 60,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-42,55; 21,37</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-51,37; 50,61</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-49,88; 46,9</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 394,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 182,0</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-54.92638858667972</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-46.94391650302908</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-56.92382958185132</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-25.79886277528573</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>36.25502425702698</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>44.06369042945877</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>42.5976235322784</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.700798494060148</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-17.84210949506665</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-13.49388328105889</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.1880754900023096</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1267235496564256</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.5984816151479372</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.4197688322360576</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.00384057884037866</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-47.06498319419204</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-42.55308967572181</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-51.37219074042317</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-49.87618022389868</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>60.6137149926754</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>21.37395318115469</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>50.61152116845984</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>46.90251933263604</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>3.944693131782777</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>1.820011147746984</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,72</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-6,18</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-46,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-45,31%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-51,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-9,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-27,8; 12,24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-17,59; 7,67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-17,39; 9,24</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-27,0; 20,78</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 222,76</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 125,79</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-73,56; 140,5</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-8.717846516673578</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-6.180163843580814</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-4.810294592019301</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.835173449622475</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.4688212380081302</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.4530603166831068</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.5120406506063031</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.09765414716386604</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-27.8022477075037</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-17.59463268895477</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-17.38626169391643</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-27.00370152054597</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>-0.7355869064404832</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>12.23666031974166</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.673652574205038</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>9.23960880562823</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>20.77990272510416</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.227600279015077</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.257855993518094</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="n">
+        <v>1.405014090350534</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1021,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
